--- a/report/TT2.xlsx
+++ b/report/TT2.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13180"/>
+    <workbookView windowWidth="30240" windowHeight="13180" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Papers" sheetId="1" r:id="rId1"/>
+    <sheet name="4 scenarios" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>STT</t>
   </si>
@@ -181,6 +182,96 @@
   </si>
   <si>
     <t>Wasm cải thiện 30%+ hiệu năng tính toán; cho phép UI phản hồi mượt mà hơn bằng cách đẩy tác vụ nặng ra khỏi luồng chính.</t>
+  </si>
+  <si>
+    <t>Kịch bản</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Grayscale</t>
+  </si>
+  <si>
+    <t>Blur</t>
+  </si>
+  <si>
+    <t>Diff/output</t>
+  </si>
+  <si>
+    <t>Mục đích</t>
+  </si>
+  <si>
+    <t>1. Scalar</t>
+  </si>
+  <si>
+    <t>motion_wasm.cpp</t>
+  </si>
+  <si>
+    <t>Float 0.299R + 0.587G + 0.114B</t>
+  </si>
+  <si>
+    <t>Box Blur 2D naive 7x7</t>
+  </si>
+  <si>
+    <t>Scalar từng pixel</t>
+  </si>
+  <si>
+    <t>Baseline WASM đơn luồng</t>
+  </si>
+  <si>
+    <t>2. SIMD</t>
+  </si>
+  <si>
+    <t>motion_wasm_simd.cpp</t>
+  </si>
+  <si>
+    <t>Integer approximation (77R + 150G + 29B) &gt;&gt; 8</t>
+  </si>
+  <si>
+    <t>Separable Blur + Sliding Window</t>
+  </si>
+  <si>
+    <t>SIMD 128-bit, 16 pixel/lệnh</t>
+  </si>
+  <si>
+    <t>Tối ưu dữ liệu + thuật toán</t>
+  </si>
+  <si>
+    <t>3. Multi-thread</t>
+  </si>
+  <si>
+    <t>motion_wasm_mt.cpp</t>
+  </si>
+  <si>
+    <t>Float như kịch bản 1</t>
+  </si>
+  <si>
+    <t>Box Blur naive như kịch bản 1</t>
+  </si>
+  <si>
+    <t>Scalar, nhưng chia 4 thread</t>
+  </si>
+  <si>
+    <t>Cô lập tác động đa luồng</t>
+  </si>
+  <si>
+    <t>4. SIMD + MT</t>
+  </si>
+  <si>
+    <t>motion_wasm_simd_mt.cpp</t>
+  </si>
+  <si>
+    <t>Integer như kịch bản 2, nhưng chạy song song</t>
+  </si>
+  <si>
+    <t>Separable Blur + Sliding Window, chạy song song</t>
+  </si>
+  <si>
+    <t>SIMD 128-bit trong 4 thread</t>
+  </si>
+  <si>
+    <t>Cộng dồn tối ưu thuật toán + SIMD + đa luồng</t>
   </si>
 </sst>
 </file>
@@ -193,8 +284,16 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
-    <font>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -700,153 +799,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1385,213 +1487,333 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="5.203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="34.8984375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.03125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.84375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.4609375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="5.203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="34.8984375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.03125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="36.84375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="33.4609375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="46.875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="41.75" spans="1:6">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="3" customFormat="1" ht="21.75" spans="1:6">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="53.75" spans="1:6">
-      <c r="A2" s="4">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="53.75" spans="1:6">
-      <c r="A3" s="4">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" ht="53.75" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" ht="71.75" spans="1:6">
-      <c r="A5" s="4">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" ht="53.75" spans="1:6">
-      <c r="A6" s="4">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" ht="53.75" spans="1:6">
-      <c r="A7" s="4">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" ht="53.75" spans="1:6">
-      <c r="A8" s="4">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" ht="53.75" spans="1:6">
-      <c r="A9" s="4">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" ht="53.75" spans="1:6">
-      <c r="A10" s="4">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="11.9765625" customWidth="1"/>
+    <col min="2" max="2" width="22.96875" customWidth="1"/>
+    <col min="3" max="3" width="38.4375" customWidth="1"/>
+    <col min="4" max="4" width="27.1875" customWidth="1"/>
+    <col min="5" max="5" width="22.96875" customWidth="1"/>
+    <col min="6" max="6" width="36.8515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" ht="68" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" ht="84" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" ht="68" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" ht="101" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/report/TT2.xlsx
+++ b/report/TT2.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13180" activeTab="1"/>
+    <workbookView windowWidth="30240" windowHeight="13180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Papers" sheetId="1" r:id="rId1"/>
     <sheet name="4 scenarios" sheetId="2" r:id="rId2"/>
+    <sheet name="Câu hỏi" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
     <t>STT</t>
   </si>
@@ -272,6 +273,266 @@
   </si>
   <si>
     <t>Cộng dồn tối ưu thuật toán + SIMD + đa luồng</t>
+  </si>
+  <si>
+    <t>so sánh các kịch bản, lượng code tăng giảm bao nhiêu, ảnh hưởng gì tới chất lượng không</t>
+  </si>
+  <si>
+    <t>định lượng: pp nghiên cứu dựa trên kết quả đo đạt được</t>
+  </si>
+  <si>
+    <t>Chuyển văn bản thành AST (Chậm) AST là gì</t>
+  </si>
+  <si>
+    <t>jitter</t>
+  </si>
+  <si>
+    <t>GC</t>
+  </si>
+  <si>
+    <t>JIT vs AOT</t>
+  </si>
+  <si>
+    <t>phân vị p99, p95</t>
+  </si>
+  <si>
+    <t>variance</t>
+  </si>
+  <si>
+    <t>speedup</t>
+  </si>
+  <si>
+    <t>Linear memory</t>
+  </si>
+  <si>
+    <t>web workers là gì</t>
+  </si>
+  <si>
+    <t>chi phí điều phối overhead</t>
+  </si>
+  <si>
+    <t>33mb: 4 byte/1 pixel màu -&gt; 4k (3840 x 2160 ~ 8.3 triệu điểm ảnh) -&gt; ~33mb / frame</t>
+  </si>
+  <si>
+    <t>60fps -&gt; 1000 (1s) / 60  = 16,667 s</t>
+  </si>
+  <si>
+    <t>độ lệch chuẩn</t>
+  </si>
+  <si>
+    <t>malloc và free trong linear memory của wasm</t>
+  </si>
+  <si>
+    <t>ở các kịch bản 2-4, dùng đa luồng (shared array buffer) thì dùng atomics để tránh race condition giữa các luồng -&gt; dùng thế nào trong code</t>
+  </si>
+  <si>
+    <t>wasm tận dụng bộ nhớ thủ công -&gt; dùng ở đâu trong cả 4 case</t>
+  </si>
+  <si>
+    <t>tại sao tận dụng SIMD lại gọi là vector hóa</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">các tập lệnh như </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wasm_u16x8_mul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wasm_simd128.h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lưu ở đâu triển khai ở đâu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>wasm_u8x16_sub_sat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (trừ có bão hòa) là gì</t>
+    </r>
+  </si>
+  <si>
+    <t>câu sau nghĩa là gì: (mục 3.4.2)</t>
+  </si>
+  <si>
+    <r>
+      <t>l </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Xử lý mặt nạ bit:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sử dụng lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wasm_u8x16_sub_sat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (trừ có bão hòa) để tính chênh lệch khung hình cho 16 pixel cùng lúc, kết hợp với các toán tử logic để tối thiểu hóa việc rẽ nhánh (branching) trong mã máy.</t>
+    </r>
+  </si>
+  <si>
+    <t>trong các kịch bản, kịch bản nào nâng cấp thuật toán</t>
+  </si>
+  <si>
+    <t>emscripten O3 là gì</t>
+  </si>
+  <si>
+    <t>tại sao kịch bản 3 và 4 dùng</t>
+  </si>
+  <si>
+    <t>Cross-Origin-Opener-Policy: same-origin</t>
+  </si>
+  <si>
+    <t>Cross-Origin-Embedder-Policy: require-corp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WebAssembly hỗ trợ thư viện </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pthreads</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chuẩn POSIX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">POSIX là Portable Operating System Interface à một bộ tiêu chuẩn kỹ thuật được đặt ra để đảm bảo tính </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tương thích</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> giữa các hệ điều hành khác nhau</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phương pháp thực nghiệm hệ thống (Systematic Experimental Method)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là cách tiếp cận khoa học để nghiên cứu một hệ thống, thay vì chỉ dựa vào lý thuyết hay suy đoán, phương pháp này dùng số liệu thực tế để chứng minh một giả thuyết.</t>
+    </r>
+  </si>
+  <si>
+    <t>Với mỗi pixel, hệ thống tính trung bình cộng của các pixel trong vùng lân cận k×k (với bán kính r=3, k=7). Độ phức tạp là O(Nk2), tương đương hơn 400 triệu phép tính cho mỗi khung hình 4K.</t>
+  </si>
+  <si>
+    <t>vì k = 2r + 1 =&gt; k=7 thì r  = 3</t>
+  </si>
+  <si>
+    <t>tại sao  O(Nk2) lại ra 400 triệu phép tính / frame: N là 8.3 triệu pixel x 49 phép tính -&gt; hơn 400 triệu phép tính / frame</t>
   </si>
 </sst>
 </file>
@@ -284,8 +545,16 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
-    <font>
+  <fonts count="25">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -799,156 +1068,168 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1487,212 +1768,212 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="5.203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="34.8984375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.03125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="36.84375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="33.4609375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="46.875" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="5.203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="34.8984375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="17.03125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="36.84375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="33.4609375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="46.875" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" ht="21.75" spans="1:6">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="7" customFormat="1" ht="21.75" spans="1:6">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="53.75" spans="1:6">
-      <c r="A2" s="6">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="53.75" spans="1:6">
-      <c r="A3" s="6">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" ht="53.75" spans="1:6">
-      <c r="A4" s="6">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" ht="71.75" spans="1:6">
-      <c r="A5" s="6">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" ht="53.75" spans="1:6">
-      <c r="A6" s="6">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" ht="53.75" spans="1:6">
-      <c r="A7" s="6">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" ht="53.75" spans="1:6">
-      <c r="A8" s="6">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="10" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" ht="53.75" spans="1:6">
-      <c r="A9" s="6">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="10" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" ht="53.75" spans="1:6">
-      <c r="A10" s="6">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1717,103 +1998,289 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" spans="1:6">
+      <c r="A1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" ht="68" spans="1:6">
+      <c r="A2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" ht="84" spans="1:6">
+      <c r="A3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" ht="68" spans="1:6">
+      <c r="A4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" ht="101" spans="1:6">
+      <c r="A5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A34"/>
+  <sheetFormatPr defaultColWidth="108.0625" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="107.5" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="108.0625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="17" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" ht="68" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" ht="84" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" ht="68" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" ht="101" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="34" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="34" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="34" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="34" spans="1:1">
+      <c r="A31" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="34" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
